--- a/2026 TD-FG League Draft Board.xlsx
+++ b/2026 TD-FG League Draft Board.xlsx
@@ -584,11 +584,11 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
     <col width="62" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -662,12 +662,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>2026 Proj Pts</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2025 Exp</t>
+          <t>2025 Pts</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Conf</t>
+          <t>Conf Lvl</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -18083,7 +18083,7 @@
     <row r="22">
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>tab and Points/VOR/Adj VOR recalculate.</t>
+          <t>tab and 2026 Proj Pts / VOR / Adj VOR recalculate.</t>
         </is>
       </c>
     </row>
@@ -18093,7 +18093,7 @@
     <row r="24">
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>2025 Exp is not a projection and not editable: it is what the player actually scored</t>
+          <t>2025 Pts is not a projection and not editable: it is what the player actually scored</t>
         </is>
       </c>
     </row>
@@ -18158,11 +18158,11 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
     <col width="62" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -18236,12 +18236,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>2026 Proj Pts</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2025 Exp</t>
+          <t>2025 Pts</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -18256,7 +18256,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Conf</t>
+          <t>Conf Lvl</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -20484,11 +20484,11 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
     <col width="62" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -20562,12 +20562,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>2026 Proj Pts</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2025 Exp</t>
+          <t>2025 Pts</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Conf</t>
+          <t>Conf Lvl</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -24779,11 +24779,11 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
     <col width="62" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -24857,12 +24857,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>2026 Proj Pts</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2025 Exp</t>
+          <t>2025 Pts</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Conf</t>
+          <t>Conf Lvl</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -29657,11 +29657,11 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
     <col width="62" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -29735,12 +29735,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>2026 Proj Pts</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2025 Exp</t>
+          <t>2025 Pts</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -29755,7 +29755,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Conf</t>
+          <t>Conf Lvl</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -31564,11 +31564,11 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
     <col width="62" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -31642,12 +31642,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>2026 Proj Pts</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2025 Exp</t>
+          <t>2025 Pts</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -31662,7 +31662,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Conf</t>
+          <t>Conf Lvl</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -33607,11 +33607,11 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
     <col width="62" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -33685,12 +33685,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>2026 Proj Pts</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2025 Exp</t>
+          <t>2025 Pts</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Conf</t>
+          <t>Conf Lvl</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
